--- a/data/asistencia/Rieleros 2026.xlsx
+++ b/data/asistencia/Rieleros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="52">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>6.67%</t>
+    <t>13.33%</t>
   </si>
   <si>
     <t>Home Oro</t>
@@ -94,25 +94,25 @@
     <t>Palco Plus Derecho</t>
   </si>
   <si>
-    <t>90.56%</t>
+    <t>92.22%</t>
   </si>
   <si>
     <t>Palco Plus izquierdo</t>
   </si>
   <si>
-    <t>87.21%</t>
+    <t>94.19%</t>
   </si>
   <si>
     <t>Preferente Derecho</t>
   </si>
   <si>
-    <t>22.29%</t>
+    <t>34.47%</t>
   </si>
   <si>
     <t>Preferente Izquierdo</t>
   </si>
   <si>
-    <t>3.45%</t>
+    <t>6.89%</t>
   </si>
   <si>
     <t>Suite</t>
@@ -124,49 +124,49 @@
     <t>Tablitas</t>
   </si>
   <si>
-    <t>8.33%</t>
+    <t>12.78%</t>
   </si>
   <si>
     <t>Terraza 1er</t>
   </si>
   <si>
-    <t>22.50%</t>
+    <t>35.50%</t>
   </si>
   <si>
     <t>Terraza 3ra</t>
   </si>
   <si>
-    <t>23.00%</t>
+    <t>54.00%</t>
   </si>
   <si>
     <t>Zona Plata</t>
   </si>
   <si>
-    <t>70.02%</t>
+    <t>87.20%</t>
   </si>
   <si>
     <t>Zona Rielera 1era.</t>
   </si>
   <si>
-    <t>47.43%</t>
+    <t>78.57%</t>
   </si>
   <si>
     <t>Zona Rielera 3ra.</t>
   </si>
   <si>
-    <t>21.39%</t>
+    <t>24.86%</t>
   </si>
   <si>
     <t>Zona VIP</t>
   </si>
   <si>
-    <t>57.17%</t>
+    <t>78.01%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>31.82%</t>
+    <t>43.15%</t>
   </si>
 </sst>
 </file>
@@ -679,7 +679,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -718,10 +718,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -791,7 +791,7 @@
         <v>180</v>
       </c>
       <c r="C8" s="6">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -826,14 +826,14 @@
       <c r="N8" s="6">
         <v>2</v>
       </c>
-      <c r="O8" s="6">
-        <v>10</v>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q8" s="6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -847,7 +847,7 @@
         <v>172</v>
       </c>
       <c r="C9" s="6">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -886,10 +886,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="Q9" s="6">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -903,13 +903,13 @@
         <v>1256</v>
       </c>
       <c r="C10" s="6">
-        <v>154</v>
+        <v>323</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -935,17 +935,17 @@
       <c r="M10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="6">
-        <v>49</v>
-      </c>
-      <c r="O10" s="6">
-        <v>2</v>
+      <c r="N10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>280</v>
+        <v>433</v>
       </c>
       <c r="Q10" s="6">
-        <v>976</v>
+        <v>823</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -959,13 +959,13 @@
         <v>1393</v>
       </c>
       <c r="C11" s="6">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -998,10 +998,10 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="Q11" s="6">
-        <v>1345</v>
+        <v>1297</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1071,13 +1071,13 @@
         <v>180</v>
       </c>
       <c r="C13" s="6">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
+      <c r="E13" s="6">
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1110,10 +1110,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q13" s="6">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1127,7 +1127,7 @@
         <v>200</v>
       </c>
       <c r="C14" s="6">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>22</v>
@@ -1162,14 +1162,14 @@
       <c r="N14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O14" s="6">
-        <v>4</v>
+      <c r="O14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="Q14" s="6">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>39</v>
@@ -1183,7 +1183,7 @@
         <v>200</v>
       </c>
       <c r="C15" s="6">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>22</v>
@@ -1222,10 +1222,10 @@
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="Q15" s="6">
-        <v>154</v>
+        <v>92</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>41</v>
@@ -1239,7 +1239,7 @@
         <v>547</v>
       </c>
       <c r="C16" s="6">
-        <v>327</v>
+        <v>430</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -1272,16 +1272,16 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>46</v>
-      </c>
-      <c r="O16" s="6">
-        <v>5</v>
+        <v>42</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>383</v>
+        <v>477</v>
       </c>
       <c r="Q16" s="6">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>43</v>
@@ -1295,7 +1295,7 @@
         <v>350</v>
       </c>
       <c r="C17" s="6">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
@@ -1330,14 +1330,14 @@
       <c r="N17" s="6">
         <v>40</v>
       </c>
-      <c r="O17" s="6">
-        <v>10</v>
+      <c r="O17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>166</v>
+        <v>275</v>
       </c>
       <c r="Q17" s="6">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>45</v>
@@ -1351,7 +1351,7 @@
         <v>346</v>
       </c>
       <c r="C18" s="6">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
@@ -1390,10 +1390,10 @@
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="Q18" s="6">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>47</v>
@@ -1407,7 +1407,7 @@
         <v>523</v>
       </c>
       <c r="C19" s="6">
-        <v>186</v>
+        <v>295</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>22</v>
@@ -1419,7 +1419,7 @@
         <v>22</v>
       </c>
       <c r="G19" s="6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
@@ -1440,16 +1440,16 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>87</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>22</v>
+        <v>81</v>
+      </c>
+      <c r="O19" s="6">
+        <v>3</v>
       </c>
       <c r="P19" s="6">
-        <v>299</v>
+        <v>408</v>
       </c>
       <c r="Q19" s="6">
-        <v>224</v>
+        <v>115</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>49</v>

--- a/data/asistencia/Rieleros 2026.xlsx
+++ b/data/asistencia/Rieleros 2026.xlsx
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>13.33%</t>
+    <t>20.00%</t>
   </si>
   <si>
     <t>Home Oro</t>
@@ -106,67 +106,67 @@
     <t>Preferente Derecho</t>
   </si>
   <si>
-    <t>34.47%</t>
+    <t>39.25%</t>
   </si>
   <si>
     <t>Preferente Izquierdo</t>
   </si>
   <si>
-    <t>6.89%</t>
+    <t>9.69%</t>
   </si>
   <si>
     <t>Suite</t>
   </si>
   <si>
-    <t>30.00%</t>
+    <t>52.00%</t>
   </si>
   <si>
     <t>Tablitas</t>
   </si>
   <si>
-    <t>12.78%</t>
+    <t>18.89%</t>
   </si>
   <si>
     <t>Terraza 1er</t>
   </si>
   <si>
-    <t>35.50%</t>
+    <t>46.00%</t>
   </si>
   <si>
     <t>Terraza 3ra</t>
   </si>
   <si>
-    <t>54.00%</t>
+    <t>57.00%</t>
   </si>
   <si>
     <t>Zona Plata</t>
   </si>
   <si>
-    <t>87.20%</t>
+    <t>94.33%</t>
   </si>
   <si>
     <t>Zona Rielera 1era.</t>
   </si>
   <si>
-    <t>78.57%</t>
+    <t>86.29%</t>
   </si>
   <si>
     <t>Zona Rielera 3ra.</t>
   </si>
   <si>
-    <t>24.86%</t>
+    <t>52.02%</t>
   </si>
   <si>
     <t>Zona VIP</t>
   </si>
   <si>
-    <t>78.01%</t>
+    <t>91.20%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>43.15%</t>
+    <t>50.46%</t>
   </si>
 </sst>
 </file>
@@ -679,7 +679,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -718,10 +718,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -735,7 +735,7 @@
         <v>60</v>
       </c>
       <c r="C7" s="6">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -791,7 +791,7 @@
         <v>180</v>
       </c>
       <c r="C8" s="6">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -823,8 +823,8 @@
       <c r="M8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="6">
-        <v>2</v>
+      <c r="N8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
@@ -865,7 +865,7 @@
         <v>22</v>
       </c>
       <c r="I9" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -880,7 +880,7 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
@@ -903,19 +903,19 @@
         <v>1256</v>
       </c>
       <c r="C10" s="6">
-        <v>323</v>
+        <v>377</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
@@ -942,10 +942,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>433</v>
+        <v>493</v>
       </c>
       <c r="Q10" s="6">
-        <v>823</v>
+        <v>763</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -959,13 +959,13 @@
         <v>1393</v>
       </c>
       <c r="C11" s="6">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -998,10 +998,10 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="Q11" s="6">
-        <v>1297</v>
+        <v>1258</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1033,7 +1033,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="6">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1054,10 +1054,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="6">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1071,13 +1071,13 @@
         <v>180</v>
       </c>
       <c r="C13" s="6">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1110,10 +1110,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Q13" s="6">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1127,7 +1127,7 @@
         <v>200</v>
       </c>
       <c r="C14" s="6">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>22</v>
@@ -1166,10 +1166,10 @@
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="Q14" s="6">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>39</v>
@@ -1183,7 +1183,7 @@
         <v>200</v>
       </c>
       <c r="C15" s="6">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>22</v>
@@ -1222,10 +1222,10 @@
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>41</v>
@@ -1239,7 +1239,7 @@
         <v>547</v>
       </c>
       <c r="C16" s="6">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -1278,10 +1278,10 @@
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="Q16" s="6">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>43</v>
@@ -1295,7 +1295,7 @@
         <v>350</v>
       </c>
       <c r="C17" s="6">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
@@ -1334,10 +1334,10 @@
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="Q17" s="6">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>45</v>
@@ -1351,7 +1351,7 @@
         <v>346</v>
       </c>
       <c r="C18" s="6">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
@@ -1384,16 +1384,16 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>40</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>22</v>
+        <v>92</v>
+      </c>
+      <c r="O18" s="6">
+        <v>2</v>
       </c>
       <c r="P18" s="6">
-        <v>86</v>
+        <v>180</v>
       </c>
       <c r="Q18" s="6">
-        <v>260</v>
+        <v>166</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>47</v>
@@ -1407,7 +1407,7 @@
         <v>523</v>
       </c>
       <c r="C19" s="6">
-        <v>295</v>
+        <v>362</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>22</v>
@@ -1443,13 +1443,13 @@
         <v>81</v>
       </c>
       <c r="O19" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P19" s="6">
-        <v>408</v>
+        <v>477</v>
       </c>
       <c r="Q19" s="6">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>49</v>

--- a/data/asistencia/Rieleros 2026.xlsx
+++ b/data/asistencia/Rieleros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="52">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,13 +88,13 @@
     <t>Home Oro</t>
   </si>
   <si>
-    <t>98.33%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Palco Plus Derecho</t>
   </si>
   <si>
-    <t>92.22%</t>
+    <t>92.78%</t>
   </si>
   <si>
     <t>Palco Plus izquierdo</t>
@@ -106,13 +106,13 @@
     <t>Preferente Derecho</t>
   </si>
   <si>
-    <t>39.25%</t>
+    <t>45.54%</t>
   </si>
   <si>
     <t>Preferente Izquierdo</t>
   </si>
   <si>
-    <t>9.69%</t>
+    <t>41.21%</t>
   </si>
   <si>
     <t>Suite</t>
@@ -124,49 +124,49 @@
     <t>Tablitas</t>
   </si>
   <si>
-    <t>18.89%</t>
+    <t>23.33%</t>
   </si>
   <si>
     <t>Terraza 1er</t>
   </si>
   <si>
-    <t>46.00%</t>
+    <t>56.50%</t>
   </si>
   <si>
     <t>Terraza 3ra</t>
   </si>
   <si>
-    <t>57.00%</t>
+    <t>76.50%</t>
   </si>
   <si>
     <t>Zona Plata</t>
   </si>
   <si>
-    <t>94.33%</t>
+    <t>97.07%</t>
   </si>
   <si>
     <t>Zona Rielera 1era.</t>
   </si>
   <si>
-    <t>86.29%</t>
+    <t>93.71%</t>
   </si>
   <si>
     <t>Zona Rielera 3ra.</t>
   </si>
   <si>
-    <t>52.02%</t>
+    <t>63.58%</t>
   </si>
   <si>
     <t>Zona VIP</t>
   </si>
   <si>
-    <t>91.20%</t>
+    <t>96.37%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>50.46%</t>
+    <t>62.84%</t>
   </si>
 </sst>
 </file>
@@ -735,7 +735,7 @@
         <v>60</v>
       </c>
       <c r="C7" s="6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -774,10 +774,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -791,7 +791,7 @@
         <v>180</v>
       </c>
       <c r="C8" s="6">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -830,10 +830,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q8" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -903,19 +903,19 @@
         <v>1256</v>
       </c>
       <c r="C10" s="6">
-        <v>377</v>
+        <v>449</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
@@ -942,10 +942,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>493</v>
+        <v>572</v>
       </c>
       <c r="Q10" s="6">
-        <v>763</v>
+        <v>684</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -959,13 +959,13 @@
         <v>1393</v>
       </c>
       <c r="C11" s="6">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>43</v>
+        <v>443</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -998,10 +998,10 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>135</v>
+        <v>574</v>
       </c>
       <c r="Q11" s="6">
-        <v>1258</v>
+        <v>819</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1071,13 +1071,13 @@
         <v>180</v>
       </c>
       <c r="C13" s="6">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1110,10 +1110,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Q13" s="6">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1127,7 +1127,7 @@
         <v>200</v>
       </c>
       <c r="C14" s="6">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>22</v>
@@ -1166,10 +1166,10 @@
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="Q14" s="6">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>39</v>
@@ -1183,7 +1183,7 @@
         <v>200</v>
       </c>
       <c r="C15" s="6">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>22</v>
@@ -1222,10 +1222,10 @@
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="Q15" s="6">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>41</v>
@@ -1239,13 +1239,13 @@
         <v>547</v>
       </c>
       <c r="C16" s="6">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>22</v>
+      <c r="E16" s="6">
+        <v>40</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1271,17 +1271,17 @@
       <c r="M16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N16" s="6">
-        <v>42</v>
+      <c r="N16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="Q16" s="6">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>43</v>
@@ -1295,13 +1295,13 @@
         <v>350</v>
       </c>
       <c r="C17" s="6">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>22</v>
+      <c r="E17" s="6">
+        <v>40</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1327,17 +1327,17 @@
       <c r="M17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="6">
-        <v>40</v>
+      <c r="N17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="Q17" s="6">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>45</v>
@@ -1351,13 +1351,13 @@
         <v>346</v>
       </c>
       <c r="C18" s="6">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>22</v>
+      <c r="E18" s="6">
+        <v>40</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1384,16 +1384,16 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>92</v>
-      </c>
-      <c r="O18" s="6">
-        <v>2</v>
+        <v>52</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="Q18" s="6">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>47</v>
@@ -1407,7 +1407,7 @@
         <v>523</v>
       </c>
       <c r="C19" s="6">
-        <v>362</v>
+        <v>412</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>22</v>
@@ -1440,16 +1440,16 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="O19" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P19" s="6">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="Q19" s="6">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>49</v>

--- a/data/asistencia/Rieleros 2026.xlsx
+++ b/data/asistencia/Rieleros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="52">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -100,19 +100,19 @@
     <t>Palco Plus izquierdo</t>
   </si>
   <si>
-    <t>94.19%</t>
+    <t>96.51%</t>
   </si>
   <si>
     <t>Preferente Derecho</t>
   </si>
   <si>
-    <t>45.54%</t>
+    <t>51.59%</t>
   </si>
   <si>
     <t>Preferente Izquierdo</t>
   </si>
   <si>
-    <t>41.21%</t>
+    <t>45.01%</t>
   </si>
   <si>
     <t>Suite</t>
@@ -124,49 +124,49 @@
     <t>Tablitas</t>
   </si>
   <si>
-    <t>23.33%</t>
+    <t>35.00%</t>
   </si>
   <si>
     <t>Terraza 1er</t>
   </si>
   <si>
-    <t>56.50%</t>
+    <t>77.00%</t>
   </si>
   <si>
     <t>Terraza 3ra</t>
   </si>
   <si>
-    <t>76.50%</t>
+    <t>93.00%</t>
   </si>
   <si>
     <t>Zona Plata</t>
   </si>
   <si>
-    <t>97.07%</t>
+    <t>98.35%</t>
   </si>
   <si>
     <t>Zona Rielera 1era.</t>
   </si>
   <si>
-    <t>93.71%</t>
+    <t>96.00%</t>
   </si>
   <si>
     <t>Zona Rielera 3ra.</t>
   </si>
   <si>
-    <t>63.58%</t>
+    <t>77.75%</t>
   </si>
   <si>
     <t>Zona VIP</t>
   </si>
   <si>
-    <t>96.37%</t>
+    <t>97.51%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>62.84%</t>
+    <t>68.14%</t>
   </si>
 </sst>
 </file>
@@ -847,7 +847,7 @@
         <v>172</v>
       </c>
       <c r="C9" s="6">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -880,16 +880,16 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q9" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -903,13 +903,13 @@
         <v>1256</v>
       </c>
       <c r="C10" s="6">
-        <v>449</v>
+        <v>504</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -942,10 +942,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>572</v>
+        <v>648</v>
       </c>
       <c r="Q10" s="6">
-        <v>684</v>
+        <v>608</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -959,13 +959,13 @@
         <v>1393</v>
       </c>
       <c r="C11" s="6">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -994,14 +994,14 @@
       <c r="N11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="6" t="s">
-        <v>22</v>
+      <c r="O11" s="6">
+        <v>4</v>
       </c>
       <c r="P11" s="6">
-        <v>574</v>
+        <v>627</v>
       </c>
       <c r="Q11" s="6">
-        <v>819</v>
+        <v>766</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1071,13 +1071,13 @@
         <v>180</v>
       </c>
       <c r="C13" s="6">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1110,10 +1110,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="6">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1127,13 +1127,13 @@
         <v>200</v>
       </c>
       <c r="C14" s="6">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
+      <c r="E14" s="6">
+        <v>4</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
@@ -1166,10 +1166,10 @@
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="Q14" s="6">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>39</v>
@@ -1183,7 +1183,7 @@
         <v>200</v>
       </c>
       <c r="C15" s="6">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>22</v>
@@ -1222,10 +1222,10 @@
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="Q15" s="6">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>41</v>
@@ -1239,7 +1239,7 @@
         <v>547</v>
       </c>
       <c r="C16" s="6">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -1274,14 +1274,14 @@
       <c r="N16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O16" s="6" t="s">
-        <v>22</v>
+      <c r="O16" s="6">
+        <v>3</v>
       </c>
       <c r="P16" s="6">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="Q16" s="6">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>43</v>
@@ -1295,7 +1295,7 @@
         <v>350</v>
       </c>
       <c r="C17" s="6">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
@@ -1334,10 +1334,10 @@
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="Q17" s="6">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>45</v>
@@ -1351,13 +1351,13 @@
         <v>346</v>
       </c>
       <c r="C18" s="6">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1384,16 +1384,16 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>52</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>22</v>
+        <v>22</v>
+      </c>
+      <c r="O18" s="6">
+        <v>2</v>
       </c>
       <c r="P18" s="6">
-        <v>220</v>
+        <v>269</v>
       </c>
       <c r="Q18" s="6">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>47</v>
@@ -1407,13 +1407,13 @@
         <v>523</v>
       </c>
       <c r="C19" s="6">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>22</v>
+      <c r="E19" s="6">
+        <v>6</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
@@ -1440,16 +1440,16 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>56</v>
-      </c>
-      <c r="O19" s="6">
-        <v>7</v>
+        <v>50</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="Q19" s="6">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>49</v>

--- a/data/asistencia/Rieleros 2026.xlsx
+++ b/data/asistencia/Rieleros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="51">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -94,7 +94,7 @@
     <t>Palco Plus Derecho</t>
   </si>
   <si>
-    <t>92.78%</t>
+    <t>93.33%</t>
   </si>
   <si>
     <t>Palco Plus izquierdo</t>
@@ -106,13 +106,13 @@
     <t>Preferente Derecho</t>
   </si>
   <si>
-    <t>51.59%</t>
+    <t>53.42%</t>
   </si>
   <si>
     <t>Preferente Izquierdo</t>
   </si>
   <si>
-    <t>45.01%</t>
+    <t>45.44%</t>
   </si>
   <si>
     <t>Suite</t>
@@ -124,21 +124,18 @@
     <t>Tablitas</t>
   </si>
   <si>
-    <t>35.00%</t>
+    <t>36.11%</t>
   </si>
   <si>
     <t>Terraza 1er</t>
   </si>
   <si>
-    <t>77.00%</t>
+    <t>95.00%</t>
   </si>
   <si>
     <t>Terraza 3ra</t>
   </si>
   <si>
-    <t>93.00%</t>
-  </si>
-  <si>
     <t>Zona Plata</t>
   </si>
   <si>
@@ -148,13 +145,13 @@
     <t>Zona Rielera 1era.</t>
   </si>
   <si>
-    <t>96.00%</t>
+    <t>96.29%</t>
   </si>
   <si>
     <t>Zona Rielera 3ra.</t>
   </si>
   <si>
-    <t>77.75%</t>
+    <t>84.97%</t>
   </si>
   <si>
     <t>Zona VIP</t>
@@ -166,7 +163,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>68.14%</t>
+    <t>70.06%</t>
   </si>
 </sst>
 </file>
@@ -791,7 +788,7 @@
         <v>180</v>
       </c>
       <c r="C8" s="6">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -830,10 +827,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q8" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -903,7 +900,7 @@
         <v>1256</v>
       </c>
       <c r="C10" s="6">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -942,10 +939,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>648</v>
+        <v>671</v>
       </c>
       <c r="Q10" s="6">
-        <v>608</v>
+        <v>585</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -959,13 +956,13 @@
         <v>1393</v>
       </c>
       <c r="C11" s="6">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -994,14 +991,14 @@
       <c r="N11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="6">
-        <v>4</v>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="Q11" s="6">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1077,7 +1074,7 @@
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1110,10 +1107,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q13" s="6">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1127,7 +1124,7 @@
         <v>200</v>
       </c>
       <c r="C14" s="6">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>22</v>
@@ -1162,14 +1159,14 @@
       <c r="N14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O14" s="6" t="s">
-        <v>22</v>
+      <c r="O14" s="6">
+        <v>4</v>
       </c>
       <c r="P14" s="6">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="Q14" s="6">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>39</v>
@@ -1183,7 +1180,7 @@
         <v>200</v>
       </c>
       <c r="C15" s="6">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>22</v>
@@ -1222,24 +1219,24 @@
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>186</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>14</v>
+        <v>200</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="6">
         <v>547</v>
       </c>
       <c r="C16" s="6">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -1274,8 +1271,8 @@
       <c r="N16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O16" s="6">
-        <v>3</v>
+      <c r="O16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P16" s="6">
         <v>538</v>
@@ -1284,18 +1281,18 @@
         <v>9</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="6">
         <v>350</v>
       </c>
       <c r="C17" s="6">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
@@ -1334,24 +1331,24 @@
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q17" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="6">
         <v>346</v>
       </c>
       <c r="C18" s="6">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
@@ -1386,22 +1383,22 @@
       <c r="N18" s="6">
         <v>22</v>
       </c>
-      <c r="O18" s="6">
-        <v>2</v>
+      <c r="O18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="Q18" s="6">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="6">
         <v>523</v>
@@ -1452,12 +1449,12 @@
         <v>13</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="7">
         <f>SUM(B6:B19)</f>
@@ -1508,7 +1505,7 @@
         <f>SUM(Q6:Q19)</f>
       </c>
       <c r="R20" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Rieleros 2026.xlsx
+++ b/data/asistencia/Rieleros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="50">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -94,7 +94,7 @@
     <t>Palco Plus Derecho</t>
   </si>
   <si>
-    <t>93.33%</t>
+    <t>94.44%</t>
   </si>
   <si>
     <t>Palco Plus izquierdo</t>
@@ -106,13 +106,13 @@
     <t>Preferente Derecho</t>
   </si>
   <si>
-    <t>53.42%</t>
+    <t>58.44%</t>
   </si>
   <si>
     <t>Preferente Izquierdo</t>
   </si>
   <si>
-    <t>45.44%</t>
+    <t>47.67%</t>
   </si>
   <si>
     <t>Suite</t>
@@ -124,22 +124,19 @@
     <t>Tablitas</t>
   </si>
   <si>
-    <t>36.11%</t>
+    <t>43.33%</t>
   </si>
   <si>
     <t>Terraza 1er</t>
   </si>
   <si>
-    <t>95.00%</t>
-  </si>
-  <si>
     <t>Terraza 3ra</t>
   </si>
   <si>
     <t>Zona Plata</t>
   </si>
   <si>
-    <t>98.35%</t>
+    <t>98.90%</t>
   </si>
   <si>
     <t>Zona Rielera 1era.</t>
@@ -151,19 +148,19 @@
     <t>Zona Rielera 3ra.</t>
   </si>
   <si>
-    <t>84.97%</t>
+    <t>86.99%</t>
   </si>
   <si>
     <t>Zona VIP</t>
   </si>
   <si>
-    <t>97.51%</t>
+    <t>98.09%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>70.06%</t>
+    <t>72.41%</t>
   </si>
 </sst>
 </file>
@@ -737,8 +734,8 @@
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
+      <c r="E7" s="6">
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -765,7 +762,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -788,7 +785,7 @@
         <v>180</v>
       </c>
       <c r="C8" s="6">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -827,10 +824,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q8" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -900,13 +897,13 @@
         <v>1256</v>
       </c>
       <c r="C10" s="6">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -939,10 +936,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>671</v>
+        <v>734</v>
       </c>
       <c r="Q10" s="6">
-        <v>585</v>
+        <v>522</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -956,13 +953,13 @@
         <v>1393</v>
       </c>
       <c r="C11" s="6">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -991,14 +988,14 @@
       <c r="N11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="6" t="s">
-        <v>22</v>
+      <c r="O11" s="6">
+        <v>10</v>
       </c>
       <c r="P11" s="6">
-        <v>633</v>
+        <v>664</v>
       </c>
       <c r="Q11" s="6">
-        <v>760</v>
+        <v>729</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1068,7 +1065,7 @@
         <v>180</v>
       </c>
       <c r="C13" s="6">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1107,10 +1104,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="Q13" s="6">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1124,7 +1121,7 @@
         <v>200</v>
       </c>
       <c r="C14" s="6">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>22</v>
@@ -1163,18 +1160,18 @@
         <v>4</v>
       </c>
       <c r="P14" s="6">
-        <v>190</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>10</v>
+        <v>200</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="6">
         <v>200</v>
@@ -1230,13 +1227,13 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="6">
         <v>547</v>
       </c>
       <c r="C16" s="6">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -1275,18 +1272,18 @@
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="Q16" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="6">
         <v>350</v>
@@ -1337,18 +1334,18 @@
         <v>13</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" s="6">
         <v>346</v>
       </c>
       <c r="C18" s="6">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
@@ -1387,24 +1384,24 @@
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="Q18" s="6">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6">
         <v>523</v>
       </c>
       <c r="C19" s="6">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>22</v>
@@ -1422,7 +1419,7 @@
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1437,24 +1434,24 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="Q19" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="7">
         <f>SUM(B6:B19)</f>
@@ -1505,7 +1502,7 @@
         <f>SUM(Q6:Q19)</f>
       </c>
       <c r="R20" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Rieleros 2026.xlsx
+++ b/data/asistencia/Rieleros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="49">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -94,37 +94,37 @@
     <t>Palco Plus Derecho</t>
   </si>
   <si>
-    <t>94.44%</t>
+    <t>96.67%</t>
   </si>
   <si>
     <t>Palco Plus izquierdo</t>
   </si>
   <si>
-    <t>96.51%</t>
+    <t>97.67%</t>
   </si>
   <si>
     <t>Preferente Derecho</t>
   </si>
   <si>
-    <t>58.44%</t>
+    <t>70.46%</t>
   </si>
   <si>
     <t>Preferente Izquierdo</t>
   </si>
   <si>
-    <t>47.67%</t>
+    <t>62.02%</t>
   </si>
   <si>
     <t>Suite</t>
   </si>
   <si>
-    <t>52.00%</t>
+    <t>58.00%</t>
   </si>
   <si>
     <t>Tablitas</t>
   </si>
   <si>
-    <t>43.33%</t>
+    <t>57.22%</t>
   </si>
   <si>
     <t>Terraza 1er</t>
@@ -136,31 +136,28 @@
     <t>Zona Plata</t>
   </si>
   <si>
-    <t>98.90%</t>
+    <t>99.45%</t>
   </si>
   <si>
     <t>Zona Rielera 1era.</t>
   </si>
   <si>
-    <t>96.29%</t>
+    <t>97.14%</t>
   </si>
   <si>
     <t>Zona Rielera 3ra.</t>
   </si>
   <si>
-    <t>86.99%</t>
+    <t>98.55%</t>
   </si>
   <si>
     <t>Zona VIP</t>
   </si>
   <si>
-    <t>98.09%</t>
-  </si>
-  <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>72.41%</t>
+    <t>80.42%</t>
   </si>
 </sst>
 </file>
@@ -785,7 +782,7 @@
         <v>180</v>
       </c>
       <c r="C8" s="6">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -824,10 +821,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q8" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -841,7 +838,7 @@
         <v>172</v>
       </c>
       <c r="C9" s="6">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -880,10 +877,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q9" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -897,13 +894,13 @@
         <v>1256</v>
       </c>
       <c r="C10" s="6">
-        <v>575</v>
+        <v>711</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -932,14 +929,14 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
+      <c r="O10" s="6">
+        <v>5</v>
       </c>
       <c r="P10" s="6">
-        <v>734</v>
+        <v>885</v>
       </c>
       <c r="Q10" s="6">
-        <v>522</v>
+        <v>371</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -953,13 +950,13 @@
         <v>1393</v>
       </c>
       <c r="C11" s="6">
-        <v>187</v>
+        <v>345</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -989,13 +986,13 @@
         <v>22</v>
       </c>
       <c r="O11" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P11" s="6">
-        <v>664</v>
+        <v>864</v>
       </c>
       <c r="Q11" s="6">
-        <v>729</v>
+        <v>529</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1014,8 +1011,8 @@
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>22</v>
+      <c r="E12" s="6">
+        <v>12</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1048,10 +1045,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="Q12" s="6">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1065,7 +1062,7 @@
         <v>180</v>
       </c>
       <c r="C13" s="6">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1104,10 +1101,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="Q13" s="6">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>
@@ -1121,7 +1118,7 @@
         <v>200</v>
       </c>
       <c r="C14" s="6">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>22</v>
@@ -1156,8 +1153,8 @@
       <c r="N14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O14" s="6">
-        <v>4</v>
+      <c r="O14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P14" s="6">
         <v>200</v>
@@ -1233,7 +1230,7 @@
         <v>547</v>
       </c>
       <c r="C16" s="6">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -1272,10 +1269,10 @@
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="Q16" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>41</v>
@@ -1289,7 +1286,7 @@
         <v>350</v>
       </c>
       <c r="C17" s="6">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
@@ -1328,10 +1325,10 @@
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q17" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>43</v>
@@ -1345,7 +1342,7 @@
         <v>346</v>
       </c>
       <c r="C18" s="6">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
@@ -1384,10 +1381,10 @@
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="Q18" s="6">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>45</v>
@@ -1401,7 +1398,7 @@
         <v>523</v>
       </c>
       <c r="C19" s="6">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>22</v>
@@ -1440,18 +1437,18 @@
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>513</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>10</v>
+        <v>523</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="7">
         <f>SUM(B6:B19)</f>
@@ -1502,7 +1499,7 @@
         <f>SUM(Q6:Q19)</f>
       </c>
       <c r="R20" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Rieleros 2026.xlsx
+++ b/data/asistencia/Rieleros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="47">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -94,39 +94,36 @@
     <t>Palco Plus Derecho</t>
   </si>
   <si>
-    <t>96.67%</t>
+    <t>99.44%</t>
   </si>
   <si>
     <t>Palco Plus izquierdo</t>
   </si>
   <si>
-    <t>97.67%</t>
+    <t>98.84%</t>
   </si>
   <si>
     <t>Preferente Derecho</t>
   </si>
   <si>
-    <t>70.46%</t>
+    <t>85.51%</t>
   </si>
   <si>
     <t>Preferente Izquierdo</t>
   </si>
   <si>
-    <t>62.02%</t>
+    <t>85.07%</t>
   </si>
   <si>
     <t>Suite</t>
   </si>
   <si>
-    <t>58.00%</t>
+    <t>64.00%</t>
   </si>
   <si>
     <t>Tablitas</t>
   </si>
   <si>
-    <t>57.22%</t>
-  </si>
-  <si>
     <t>Terraza 1er</t>
   </si>
   <si>
@@ -136,19 +133,16 @@
     <t>Zona Plata</t>
   </si>
   <si>
-    <t>99.45%</t>
-  </si>
-  <si>
     <t>Zona Rielera 1era.</t>
   </si>
   <si>
-    <t>97.14%</t>
+    <t>99.71%</t>
   </si>
   <si>
     <t>Zona Rielera 3ra.</t>
   </si>
   <si>
-    <t>98.55%</t>
+    <t>99.42%</t>
   </si>
   <si>
     <t>Zona VIP</t>
@@ -157,7 +151,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>80.42%</t>
+    <t>91.46%</t>
   </si>
 </sst>
 </file>
@@ -782,7 +776,7 @@
         <v>180</v>
       </c>
       <c r="C8" s="6">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -821,10 +815,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="Q8" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -838,7 +832,7 @@
         <v>172</v>
       </c>
       <c r="C9" s="6">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -877,10 +871,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q9" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -894,13 +888,13 @@
         <v>1256</v>
       </c>
       <c r="C10" s="6">
-        <v>711</v>
+        <v>860</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -930,13 +924,13 @@
         <v>22</v>
       </c>
       <c r="O10" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P10" s="6">
-        <v>885</v>
+        <v>1074</v>
       </c>
       <c r="Q10" s="6">
-        <v>371</v>
+        <v>182</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -950,13 +944,13 @@
         <v>1393</v>
       </c>
       <c r="C11" s="6">
-        <v>345</v>
+        <v>619</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>507</v>
+        <v>559</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -986,13 +980,13 @@
         <v>22</v>
       </c>
       <c r="O11" s="6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P11" s="6">
-        <v>864</v>
+        <v>1185</v>
       </c>
       <c r="Q11" s="6">
-        <v>529</v>
+        <v>208</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1012,7 +1006,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1045,10 +1039,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="Q12" s="6">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1062,13 +1056,13 @@
         <v>180</v>
       </c>
       <c r="C13" s="6">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1097,22 +1091,22 @@
       <c r="N13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
+      <c r="O13" s="6">
+        <v>1</v>
       </c>
       <c r="P13" s="6">
-        <v>103</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>77</v>
+        <v>180</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="6">
         <v>200</v>
@@ -1168,7 +1162,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="6">
         <v>200</v>
@@ -1224,13 +1218,13 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="6">
         <v>547</v>
       </c>
       <c r="C16" s="6">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -1269,24 +1263,24 @@
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>544</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>3</v>
+        <v>547</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B17" s="6">
         <v>350</v>
       </c>
       <c r="C17" s="6">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
@@ -1325,24 +1319,24 @@
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="Q17" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B18" s="6">
         <v>346</v>
       </c>
       <c r="C18" s="6">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
@@ -1381,30 +1375,30 @@
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q18" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B19" s="6">
         <v>523</v>
       </c>
       <c r="C19" s="6">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E19" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
@@ -1431,7 +1425,7 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
@@ -1448,7 +1442,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" s="7">
         <f>SUM(B6:B19)</f>
@@ -1499,7 +1493,7 @@
         <f>SUM(Q6:Q19)</f>
       </c>
       <c r="R20" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Rieleros 2026.xlsx
+++ b/data/asistencia/Rieleros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="42">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -94,31 +94,22 @@
     <t>Palco Plus Derecho</t>
   </si>
   <si>
-    <t>99.44%</t>
-  </si>
-  <si>
     <t>Palco Plus izquierdo</t>
   </si>
   <si>
-    <t>98.84%</t>
-  </si>
-  <si>
     <t>Preferente Derecho</t>
   </si>
   <si>
-    <t>85.51%</t>
-  </si>
-  <si>
     <t>Preferente Izquierdo</t>
   </si>
   <si>
-    <t>85.07%</t>
+    <t>99.50%</t>
   </si>
   <si>
     <t>Suite</t>
   </si>
   <si>
-    <t>64.00%</t>
+    <t>65.50%</t>
   </si>
   <si>
     <t>Tablitas</t>
@@ -136,22 +127,16 @@
     <t>Zona Rielera 1era.</t>
   </si>
   <si>
-    <t>99.71%</t>
-  </si>
-  <si>
     <t>Zona Rielera 3ra.</t>
   </si>
   <si>
-    <t>99.42%</t>
-  </si>
-  <si>
     <t>Zona VIP</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>91.46%</t>
+    <t>98.43%</t>
   </si>
 </sst>
 </file>
@@ -776,7 +761,7 @@
         <v>180</v>
       </c>
       <c r="C8" s="6">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -815,24 +800,24 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>179</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="6">
         <v>172</v>
       </c>
       <c r="C9" s="6">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -871,30 +856,30 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>170</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>2</v>
+        <v>172</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6">
         <v>1256</v>
       </c>
       <c r="C10" s="6">
-        <v>860</v>
+        <v>1003</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -923,34 +908,34 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6">
-        <v>9</v>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>1074</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>182</v>
+        <v>1256</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6">
         <v>1393</v>
       </c>
       <c r="C11" s="6">
-        <v>619</v>
+        <v>770</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="6">
-        <v>559</v>
+        <v>615</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -979,22 +964,22 @@
       <c r="N11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="6">
-        <v>6</v>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>1185</v>
+        <v>1386</v>
       </c>
       <c r="Q11" s="6">
-        <v>208</v>
+        <v>7</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6">
         <v>200</v>
@@ -1006,7 +991,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1039,18 +1024,18 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q12" s="6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
         <v>180</v>
@@ -1062,7 +1047,7 @@
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1091,8 +1076,8 @@
       <c r="N13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O13" s="6">
-        <v>1</v>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P13" s="6">
         <v>180</v>
@@ -1106,7 +1091,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B14" s="6">
         <v>200</v>
@@ -1162,7 +1147,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6">
         <v>200</v>
@@ -1218,7 +1203,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B16" s="6">
         <v>547</v>
@@ -1274,13 +1259,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6">
         <v>350</v>
       </c>
       <c r="C17" s="6">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
@@ -1319,30 +1304,30 @@
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>349</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>1</v>
+        <v>350</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6">
         <v>346</v>
       </c>
       <c r="C18" s="6">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="6">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1369,24 +1354,24 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>344</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>2</v>
+        <v>346</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6">
         <v>523</v>
@@ -1398,7 +1383,7 @@
         <v>22</v>
       </c>
       <c r="E19" s="6">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
@@ -1425,7 +1410,7 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
@@ -1442,7 +1427,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B20" s="7">
         <f>SUM(B6:B19)</f>
@@ -1493,7 +1478,7 @@
         <f>SUM(Q6:Q19)</f>
       </c>
       <c r="R20" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
